--- a/Desglose_Ventas_Diciembre_2026_PL_1321k.xlsx
+++ b/Desglose_Ventas_Diciembre_2026_PL_1321k.xlsx
@@ -506,7 +506,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K1267"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
